--- a/artfynd/A 31881-2023 artfynd.xlsx
+++ b/artfynd/A 31881-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128549973</v>
       </c>
       <c r="B2" t="n">
-        <v>44817</v>
+        <v>44819</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31881-2023 artfynd.xlsx
+++ b/artfynd/A 31881-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128549973</v>
       </c>
       <c r="B2" t="n">
-        <v>44819</v>
+        <v>44846</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31881-2023 artfynd.xlsx
+++ b/artfynd/A 31881-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128549973</v>
       </c>
       <c r="B2" t="n">
-        <v>44846</v>
+        <v>44847</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31881-2023 artfynd.xlsx
+++ b/artfynd/A 31881-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128549973</v>
       </c>
       <c r="B2" t="n">
-        <v>44847</v>
+        <v>44850</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31881-2023 artfynd.xlsx
+++ b/artfynd/A 31881-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128549973</v>
+        <v>128549969</v>
       </c>
       <c r="B2" t="n">
-        <v>44850</v>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102019</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Klubbsprötad bastardsvärmare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Zygaena minos</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584284</v>
+        <v>584399</v>
       </c>
       <c r="R2" t="n">
-        <v>6318697</v>
+        <v>6318951</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,32 +791,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128549970</v>
+        <v>128549959</v>
       </c>
       <c r="B3" t="n">
-        <v>5197</v>
+        <v>9178</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>101595</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Aspstumpbagge</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Platysoma deplanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyllenhal, 1808)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584415</v>
+        <v>584326</v>
       </c>
       <c r="R3" t="n">
-        <v>6318805</v>
+        <v>6318708</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>06:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>06:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,6 +900,354 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>Smedmossen solpark NVI 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128549958</v>
+      </c>
+      <c r="B4" t="n">
+        <v>7166</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>101783</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tvåtandad plattbagge</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Silvanus bidentatus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1792)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Smedmossen, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>584328</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6318709</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>06:48</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>06:48</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Julia Svensson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Håkan Andersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Smedmossen solpark NVI 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128549973</v>
+      </c>
+      <c r="B5" t="n">
+        <v>45045</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102019</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Klubbsprötad bastardsvärmare</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Zygaena minos</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Smedmossen, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>584284</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6318697</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Julia Svensson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Håkan Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Smedmossen solpark NVI 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128549970</v>
+      </c>
+      <c r="B6" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Smedmossen, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>584415</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6318805</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Julia Svensson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Håkan Andersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
         <is>
           <t>Smedmossen solpark NVI 2025</t>
         </is>

--- a/artfynd/A 31881-2023 artfynd.xlsx
+++ b/artfynd/A 31881-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>Smedmossen solpark NVI 2025</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128549969</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
           <t>Smedmossen solpark NVI 2025</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128549959</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
           <t>Smedmossen solpark NVI 2025</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128549958</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1136,6 +1156,11 @@
           <t>Smedmossen solpark NVI 2025</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128549973</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1252,8 +1277,20 @@
           <t>Smedmossen solpark NVI 2025</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128549970</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>